--- a/results/job_matches_2026-06-11.xlsx
+++ b/results/job_matches_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS/ETL)</t>
+          <t>Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f3815d6e6ed4de</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e12084d35df615</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>GCP DATA ENGINEER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85cdeb8503f6c459</t>
+          <t>https://www.indeed.com/viewjob?jk=e23ead1703b573ed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Senior Software Development/Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e12084d35df615</t>
+          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP DATA ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23ead1703b573ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1badc32639c60a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior ML Engineer / MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8577c851254cde7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67874b8838f9d9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Luminie Studio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
+          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
+          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RELTIO INTEGRATION HUB ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ernest Talent</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
+          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>State of Arizona</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Informatica PowerCenter</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer .Net Full-Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8584f1ea91ecab5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c5e09077e276bd</t>
+          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
+          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, ECS, IAM, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
+          <t>https://www.indeed.com/viewjob?jk=67874b8838f9d9a8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Qeexo, Co.</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Clemente, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=631e7de01157a1c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>DevOps Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
+          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence Data Engineer</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
+          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Luminie Studio</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf16b4c9308524a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
+          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>RELTIO INTEGRATION HUB ENGINEER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Ernest Talent</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
+          <t>Azure Databrciks Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2056a1e51decf7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Enterprise Data &amp; AI Platform Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>State of Arizona</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
+          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Cloud Platform)</t>
+          <t>Senior Engineer .Net Full-Stack</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Teambuilder</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d34ade42ca5e88</t>
+          <t>https://www.indeed.com/viewjob?jk=d8584f1ea91ecab5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=73c5e09077e276bd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mid-Level -Looker Developer -Google</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33054d955a48903</t>
+          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3ba3c7c3645334</t>
+          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e500cf88e638ac7b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef1bee76953de15</t>
+          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Qeexo, Co.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Clemente, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e996475c9120b1</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
+          <t>Sr Data Architect, Databricks</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c95bf56aa2f1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Cloud Database Administrator (DBA) Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
+          <t>https://www.indeed.com/viewjob?jk=edc462ae0be8211d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 (Contractor) 529701735</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT, Tableau</t>
+          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b55eb58f3e1bbe2</t>
+          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
+          <t>https://www.indeed.com/viewjob?jk=caf16b4c9308524a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Artificial Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belews Creek, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
+          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (On Site-Only)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New York Cancer and Blood Specialists</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ridge, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, HDFS, Hive, Spark, Scala, PostgreSQL, Data Modeling, MLOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc750ce13952bfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Breakthrough)</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETL Engineer_Woonsocket, RI</t>
+          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
+          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Full Stack Senior Developer/Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3684f4d626ff94f</t>
+          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Full Stack Senior Developer/Architect</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Axiom Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Azure, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e87ee2317bc76f</t>
+          <t>https://www.indeed.com/viewjob?jk=b276af599e88a7af</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, IAM, RDS, GCP, Dataflow, Kafka, MongoDB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8932a72fefee23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architecture – Advisor II</t>
+          <t>Cloud Solutions Architect 3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3ba3c7c3645334</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b152b5aa55d165</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=9873a5dcfe8027b5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0edad65551ccdff</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=613c249c08b74171</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Belews Creek, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior DevOps Engineer (On Site-Only)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>New York Cancer and Blood Specialists</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ridge, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, EMR, S3, HDFS, Hive, Spark, Scala, PostgreSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
+          <t>https://www.indeed.com/viewjob?jk=dc750ce13952bfd8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>EMS Systems Analyst Sr</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4e9787cfc7115385</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
+          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
+          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
+          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
+          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
+          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
+          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
+          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
+          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
+          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
+          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
+          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
+          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
+          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
+          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
         </is>
       </c>
     </row>
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
+          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Analytics Data Engineer</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
+          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Analytics Engineer, AV Safety Engineering</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
+          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Holistic Partners</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
+          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer – Data Integration (Remote)</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,102 +3751,102 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
+          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
+          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer, Clinical Intelligence</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MEDecision</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,102 +3856,102 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd899653b72bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Associate Application Engineer – AI &amp; Data</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PaceMate™</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Manger, Data Engineering</t>
+          <t>Data Architecture – Advisor II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Data Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer, AV Safety Engineering</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Identity Management Engineer III</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Holistic Partners</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>Data Engineer – Data Integration (Remote)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
+          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
+          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,59 +4346,59 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Associate Application Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>PaceMate™</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
+          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Application Developer – Microsoft .NET (Remote)</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
+          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
+          <t>Senior Manger, Data Engineering</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,42 +4476,42 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
+          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Zillow</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
+          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
+          <t>Product Engineer Data &amp; AI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,67 +4591,67 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>ETL Developer - On-Site Contract</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
+          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,19 +4661,19 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfba46a758bb1aa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
+          <t>Identity Management Engineer III</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4682,11 +4682,11 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,137 +4696,137 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
+          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Insights - Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ollion</t>
+          <t>Class Boxes Technologies</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, MongoDB, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b659e64be3d4e6</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffab2e7330a09b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr. Appian Systems Administrator</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b35afbe7938db70</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, Talend</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc5438c12ec9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Java Senior Developer</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,172 +4906,172 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ebe266e21e63ac</t>
+          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Scala, ELT, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8910d769e637e7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Scala, ELT, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e6175a2dcd61b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Scala, ELT, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31841b8cf3b4d68</t>
+          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Technology Data Analyst</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Lamb Weston</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Scala, ELT, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded756039a0a140f</t>
+          <t>https://www.indeed.com/viewjob?jk=819a863aec01dded</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full Stack- FDE EST</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jessup, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a24df4c2a49d56a</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Application Developer – Microsoft .NET (Remote)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
+          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
+          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>Zillow</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
+          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
+          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Priwils</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
+          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Automation Test Engineer</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
+          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer, Engineering Applications</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,17 +5351,507 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Cloud Engineer II</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CoorsTek</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Lower</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>UserGems</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, Scala, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc9835c6151bce1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Application Developer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>California Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Athena, RDS, GCP, Hive, PostgreSQL, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d616f14c352000bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>AeroVironment</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Jessup, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Priwils</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Adelphi, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Software Engineer, Engineering Applications</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Recursion Technologies, Inc</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior OAS/ODI Developer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>International Logic Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Fairfax, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-11.xlsx
+++ b/results/job_matches_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67874b8838f9d9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631e7de01157a1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Infrastructure</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
+          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Luminie Studio</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
+          <t>Senior Data Engineer (Hybrid Eligible*)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Luminie Studio</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
+          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>RELTIO INTEGRATION HUB ENGINEER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
+          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RELTIO INTEGRATION HUB ENGINEER</t>
+          <t>Azure Databrciks Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2056a1e51decf7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
+          <t>Enterprise Data &amp; AI Platform Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ernest Talent</t>
+          <t>State of Arizona</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Databrciks Architect</t>
+          <t>Senior Engineer .Net Full-Stack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2056a1e51decf7</t>
+          <t>https://www.indeed.com/viewjob?jk=d8584f1ea91ecab5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Platform Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State of Arizona</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
+          <t>https://www.indeed.com/viewjob?jk=73c5e09077e276bd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer .Net Full-Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8584f1ea91ecab5</t>
+          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c5e09077e276bd</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
+          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Qeexo, Co.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>San Clemente, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Sr Data Architect, Databricks</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Inn-Flow Inc.</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
+          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
+          <t>https://www.indeed.com/viewjob?jk=caf16b4c9308524a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Artificial Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Qeexo, Co.</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Clemente, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Architect, Databricks</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator (DBA) Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc462ae0be8211d</t>
+          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,77 +1921,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
+          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>o9 Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf16b4c9308524a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence Data Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, Dataflow, Kafka, MongoDB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8932a72fefee23</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Cloud Solutions Architect 3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3ba3c7c3645334</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b152b5aa55d165</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9873a5dcfe8027b5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Axiom Bank</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Azure, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b276af599e88a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=b0edad65551ccdff</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Dataflow, Kafka, MongoDB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8932a72fefee23</t>
+          <t>https://www.indeed.com/viewjob?jk=613c249c08b74171</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Belews Creek, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3ba3c7c3645334</t>
+          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior DevOps Engineer (On Site-Only)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>New York Cancer and Blood Specialists</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Ridge, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
+          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>EMS Systems Analyst Sr</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b152b5aa55d165</t>
+          <t>https://www.indeed.com/viewjob?jk=4e9787cfc7115385</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9873a5dcfe8027b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0edad65551ccdff</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Data Architecture – Advisor II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c249c08b74171</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belews Creek, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (On Site-Only)</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>New York Cancer and Blood Specialists</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ridge, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
+          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, HDFS, Hive, Spark, Scala, PostgreSQL, Data Modeling, MLOps</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc750ce13952bfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EMS Systems Analyst Sr</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e9787cfc7115385</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Data &amp; Analytics</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
+          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
+          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
+          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
+          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
+          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
+          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
+          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
+          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
+          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
+          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
+          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
+          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
+          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
+          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
+          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
+          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
+          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
+          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
         </is>
       </c>
     </row>
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Engineer with Python and React - Remote</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Analytics Engineer, AV Safety Engineering</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
+          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Holistic Partners</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Data Engineer – Data Integration (Remote)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,59 +3996,59 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
+          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Architecture – Advisor II</t>
+          <t>Database Platform Distinguished Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
+          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Analytics Data Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Analytics Engineer, AV Safety Engineering</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Holistic Partners</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
+          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
+          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer – Data Integration (Remote)</t>
+          <t>Senior Manger, Data Engineering</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Product Engineer Data &amp; AI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>ETL Developer - On-Site Contract</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,59 +4346,59 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Associate Application Engineer – AI &amp; Data</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PaceMate™</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfba46a758bb1aa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Identity Management Engineer III</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
+          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Manger, Data Engineering</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technology Data Analyst</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Lamb Weston</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
+          <t>https://www.indeed.com/viewjob?jk=819a863aec01dded</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Product Engineer Data &amp; AI</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site Contract</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
+          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfba46a758bb1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Identity Management Engineer III</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
+          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>Application Developer – Microsoft .NET (Remote)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,67 +4766,67 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
+          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Class Boxes Technologies</t>
+          <t>Zillow</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, MongoDB, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffab2e7330a09b</t>
+          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tulane University</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,102 +4871,102 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
+          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,67 +4976,67 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
+          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Technology Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lamb Weston</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,19 +5046,19 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819a863aec01dded</t>
+          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Full Stack- FDE EST</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Inabia Software &amp; Consulting Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5067,11 +5067,11 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,89 +5081,89 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a24df4c2a49d56a</t>
+          <t>https://www.indeed.com/viewjob?jk=9277248c547d05a6</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Application Developer – Microsoft .NET (Remote)</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
+          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
+          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Zillow</t>
+          <t>UserGems</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
+          <t>AWS, S3, IAM, Azure, Scala, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9835c6151bce1e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>California Institute of Technology</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Athena, RDS, GCP, Hive, PostgreSQL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb4f31db86d8854</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Jessup, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
+          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
+          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,29 +5316,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
+          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Software Engineer, Engineering Applications</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
+          <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,427 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>UserGems</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, Scala, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9835c6151bce1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Application Developer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>California Institute of Technology</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Pasadena, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, GCP, Hive, PostgreSQL, CI/CD, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d616f14c352000bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>AeroVironment</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Jessup, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Priwils</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Adelphi, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Java Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Software Engineer, Engineering Applications</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Recursion Technologies, Inc</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior OAS/ODI Developer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>International Logic Systems, Inc.</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Fairfax, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-11.xlsx
+++ b/results/job_matches_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP DATA ENGINEER</t>
+          <t>Data Engineer-Marketing Technology</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Foxit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23ead1703b573ed</t>
+          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Development/Data Engineer</t>
+          <t>GCP DATA ENGINEER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
+          <t>https://www.indeed.com/viewjob?jk=e23ead1703b573ed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development/Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=99ffb50aa63952c2</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
+          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
+          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
+          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
+          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
+          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
+          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
+          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
+          <t>DevOps Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Luminie Studio</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid Eligible*)</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
+          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer (Hybrid Eligible*)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
+          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RELTIO INTEGRATION HUB ENGINEER</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
+          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure Databrciks Architect</t>
+          <t>RELTIO INTEGRATION HUB ENGINEER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2056a1e51decf7</t>
+          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
         </is>
       </c>
     </row>
@@ -1553,25 +1553,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c5e09077e276bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Inn-Flow Inc.</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
+          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr Data Architect, Databricks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
+          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qeexo, Co.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Clemente, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=caf16b4c9308524a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Data Architect, Databricks</t>
+          <t>Senior Artificial Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf16b4c9308524a</t>
+          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
+          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
         </is>
       </c>
     </row>
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
+          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>o9 Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>o9 Solutions</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, GCP, Dataflow, Kafka, MongoDB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8932a72fefee23</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Dataflow, Kafka, MongoDB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8932a72fefee23</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b152b5aa55d165</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3ba3c7c3645334</t>
+          <t>https://www.indeed.com/viewjob?jk=9873a5dcfe8027b5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b0edad65551ccdff</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b152b5aa55d165</t>
+          <t>https://www.indeed.com/viewjob?jk=613c249c08b74171</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Belews Creek, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9873a5dcfe8027b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Senior DevOps Engineer (On Site-Only)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>New York Cancer and Blood Specialists</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Ridge, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0edad65551ccdff</t>
+          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c249c08b74171</t>
+          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belews Creek, NC, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (On Site-Only)</t>
+          <t>Data Architecture – Advisor II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New York Cancer and Blood Specialists</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ridge, NY, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EMS Systems Analyst Sr</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e9787cfc7115385</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Data &amp; Analytics</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
+          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architecture – Advisor II</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
+          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
+          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
+          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
+          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
+          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
+          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
+          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
+          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
+          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
+          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
+          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
+          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
+          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
+          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
+          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
         </is>
       </c>
     </row>
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Engineer with Python and React - Remote</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Analytics Engineer, AV Safety Engineering</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Holistic Partners</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
+          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer with Python and React - Remote</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Analytics Data Engineer</t>
+          <t>Data Engineer – Data Integration (Remote)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Analytics Engineer, AV Safety Engineering</t>
+          <t>Database Platform Distinguished Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
+          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Holistic Partners</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
+          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer – Data Integration (Remote)</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,67 +3996,67 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
+          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Database Platform Distinguished Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
+          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
+          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Senior Manger, Data Engineering</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Engineer Data &amp; AI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Manger, Data Engineering</t>
+          <t>ETL Developer - On-Site Contract</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfba46a758bb1aa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Identity Management Engineer III</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
+          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Product Engineer Data &amp; AI</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site Contract</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Technology Data Analyst</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Lamb Weston</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfba46a758bb1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=819a863aec01dded</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Identity Management Engineer III</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
+          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tulane University</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Technology Data Analyst</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Lamb Weston</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Power BI, CI/CD</t>
+          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819a863aec01dded</t>
+          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Zillow</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
+          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,102 +4661,102 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
+          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Application Developer – Microsoft .NET (Remote)</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Zillow</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
+          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
+          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c76841faa3e2ec24</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6cd27db279cc95e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
+          <t>https://www.indeed.com/viewjob?jk=87468e85f996fc02</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f93a7daa5f60c1ca</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9170b1fc1f9c04</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b31324b6d66182</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Inabia Software &amp; Consulting Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9277248c547d05a6</t>
+          <t>https://www.indeed.com/viewjob?jk=57ac051678a5d39e</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3958fe987565e7d6</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
+          <t>https://www.indeed.com/viewjob?jk=20575479ac0054a4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>UserGems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Scala, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9835c6151bce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=04bb514886baf37e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>California Institute of Technology</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, GCP, Hive, PostgreSQL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb4f31db86d8854</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab4b92177ab2a8f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Jessup, MD, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
+          <t>https://www.indeed.com/viewjob?jk=ce41d6460ea15565</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
+          <t>https://www.indeed.com/viewjob?jk=539827ac7f0eff42</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
+          <t>https://www.indeed.com/viewjob?jk=60cc7bd7dd2de932</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4199a58d952d0b71</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineer, Engineering Applications</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
+          <t>https://www.indeed.com/viewjob?jk=b27686d3fff222ce</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,17 +5421,1592 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0e757b3e935e868</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ea516f27762f34d</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2bf1b37c46622cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b093a06e94f20f9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5617614ed464167</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2224a0c3978e6c38</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=732c6c249f9d73c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69acac44ec199716</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=122385d4dadbc41e</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917e38446999456c</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96c34b9216cdad10</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e26c8b42dcd2f366</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=712e8c299b3256ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0229878a0d1503c</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2479d8bb3713b04b</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=684321b06ebc10db</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=888104a1629976bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62c2b94110d9cab5</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c18f439127c3b09d</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f9ba3224629290a</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3a92dacb6f0c06e</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8777c1f859facbd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdc56720f97140d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90e498a115d128d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8c2864f998fc6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb86b3b19b4a8068</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00b790d93392a179</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=662e9fa60bd06133</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99d9cd4813e4e05f</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b101e90c86c4fe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f75f93a5375c0579</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc953ebe610d8912</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=544b450a5ce07df4</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98bc7ef959a956c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=360f723cdd8aa089</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Inabia Software &amp; Consulting Inc.</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9277248c547d05a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>UserGems</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, Scala, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc9835c6151bce1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer - Active IQ Engineering</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Application Developer</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>California Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, Athena, RDS, GCP, Hive, PostgreSQL, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fb4f31db86d8854</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>AeroVironment</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Jessup, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Recursion Technologies, Inc</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
           <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Software Engineer, Engineering Applications</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-11.xlsx
+++ b/results/job_matches_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pavago</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,129 +496,129 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424cfabc18b01038</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e12084d35df615</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Data Engineer-Marketing Technology</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Foxit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e12084d35df615</t>
+          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer-Marketing Technology</t>
+          <t>Senior Software Development/Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Foxit</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
+          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP DATA ENGINEER</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23ead1703b573ed</t>
+          <t>https://www.indeed.com/viewjob?jk=9d09a1b90b86ef4e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Development/Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,52 +626,52 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
+          <t>https://www.indeed.com/viewjob?jk=99ffb50aa63952c2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ffb50aa63952c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
+          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
+          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
+          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
+          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
+          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
+          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
+          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Infrastructure</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
         </is>
       </c>
     </row>
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
+          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
+          <t>Data Engineer/Associate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Seattle Children's</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe630ebf9cbab80</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RELTIO INTEGRATION HUB ENGINEER</t>
+          <t>Enterprise Data &amp; AI Platform Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>State of Arizona</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
+          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Platform Architect</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State of Arizona</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Informatica PowerCenter</t>
+          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer .Net Full-Stack</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8584f1ea91ecab5</t>
+          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec9eccd457d1c7e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Artificial Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Inn-Flow Inc.</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
+          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
+          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Architect, Databricks</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>o9 Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf16b4c9308524a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence Data Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>I2E Consulting Pvt Ltd</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=650af1c5e8c39884</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>o9 Solutions</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b152b5aa55d165</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=9873a5dcfe8027b5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
+          <t>https://www.indeed.com/viewjob?jk=b0edad65551ccdff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=613c249c08b74171</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Belews Creek, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Dataflow, Kafka, MongoDB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8932a72fefee23</t>
+          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b152b5aa55d165</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Data Architecture – Advisor II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9873a5dcfe8027b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0edad65551ccdff</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c249c08b74171</t>
+          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belews Creek, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
+          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (On Site-Only)</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>New York Cancer and Blood Specialists</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ridge, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Data &amp; Analytics</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Architecture – Advisor II</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
+          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
+          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
+          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
+          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
+          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
+          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
+          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
+          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
+          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
+          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
+          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
+          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
+          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
+          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
+          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
+          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
         </is>
       </c>
     </row>
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Engineer with Python and React - Remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Analytics Engineer, AV Safety Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
+          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Back-End Developer – Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, Scala, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
+          <t>https://www.indeed.com/viewjob?jk=323c21bf380dde66</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr Data Architect, Databricks</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,59 +3611,59 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Database Platform Distinguished Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
+          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer with Python and React - Remote</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analytics Data Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Analytics Engineer, AV Safety Engineering</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
+          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Software Engineer, Financial Platform</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Holistic Partners</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,77 +3776,77 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
+          <t>https://www.indeed.com/viewjob?jk=9dda4e17d3658df2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
+          <t>https://www.indeed.com/viewjob?jk=ac20b554f3336983</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer – Data Integration (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,102 +3856,102 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
+          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Database Platform Distinguished Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
+          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AlpacaJapan株式会社</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>Google Cloud Platform, GCP, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
+          <t>https://www.indeed.com/viewjob?jk=45b7132352f20af8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Product Engineer Data &amp; AI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>ETL Developer - On-Site Contract</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfba46a758bb1aa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Identity Management Engineer III</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
+          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Manger, Data Engineering</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Product Engineer Data &amp; AI</t>
+          <t>Technology Data Analyst</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Lamb Weston</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
+          <t>https://www.indeed.com/viewjob?jk=819a863aec01dded</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site Contract</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
+          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfba46a758bb1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Identity Management Engineer III</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Sr. AI &amp; Data Engineer–Trading Analytics</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Shell Energy Retail</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
+          <t>https://www.indeed.com/viewjob?jk=f379cc52c6dc1b7b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Zillow</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
+          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technology Data Analyst</t>
+          <t>BI Developer II</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Lamb Weston</t>
+          <t>Sound Physicians</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,67 +4381,67 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819a863aec01dded</t>
+          <t>https://www.indeed.com/viewjob?jk=34aa94cc9031fce2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tulane University</t>
+          <t>AlpacaJapan株式会社</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f9bcf7a0cd9dbd</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
+          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,67 +4486,67 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,19 +4556,19 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
+          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
+          <t>Senior Software Engineer - Tax Platform</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Zillow</t>
+          <t>AlpacaJapan株式会社</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
+          <t>AWS, Step Functions, Spark, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6ade65b566a785</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
+          <t>https://www.indeed.com/viewjob?jk=c76841faa3e2ec24</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a6cd27db279cc95e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
+          <t>https://www.indeed.com/viewjob?jk=87468e85f996fc02</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
+          <t>https://www.indeed.com/viewjob?jk=f93a7daa5f60c1ca</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9170b1fc1f9c04</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b31324b6d66182</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
+          <t>https://www.indeed.com/viewjob?jk=57ac051678a5d39e</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76841faa3e2ec24</t>
+          <t>https://www.indeed.com/viewjob?jk=3958fe987565e7d6</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6cd27db279cc95e</t>
+          <t>https://www.indeed.com/viewjob?jk=20575479ac0054a4</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87468e85f996fc02</t>
+          <t>https://www.indeed.com/viewjob?jk=04bb514886baf37e</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93a7daa5f60c1ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab4b92177ab2a8f</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9170b1fc1f9c04</t>
+          <t>https://www.indeed.com/viewjob?jk=ce41d6460ea15565</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b31324b6d66182</t>
+          <t>https://www.indeed.com/viewjob?jk=539827ac7f0eff42</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ac051678a5d39e</t>
+          <t>https://www.indeed.com/viewjob?jk=60cc7bd7dd2de932</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3958fe987565e7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4199a58d952d0b71</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20575479ac0054a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b27686d3fff222ce</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04bb514886baf37e</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e757b3e935e868</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab4b92177ab2a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea516f27762f34d</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce41d6460ea15565</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf1b37c46622cd</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539827ac7f0eff42</t>
+          <t>https://www.indeed.com/viewjob?jk=b093a06e94f20f9a</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60cc7bd7dd2de932</t>
+          <t>https://www.indeed.com/viewjob?jk=d5617614ed464167</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4199a58d952d0b71</t>
+          <t>https://www.indeed.com/viewjob?jk=2224a0c3978e6c38</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27686d3fff222ce</t>
+          <t>https://www.indeed.com/viewjob?jk=732c6c249f9d73c5</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e757b3e935e868</t>
+          <t>https://www.indeed.com/viewjob?jk=69acac44ec199716</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea516f27762f34d</t>
+          <t>https://www.indeed.com/viewjob?jk=122385d4dadbc41e</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf1b37c46622cd</t>
+          <t>https://www.indeed.com/viewjob?jk=917e38446999456c</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b093a06e94f20f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=96c34b9216cdad10</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5617614ed464167</t>
+          <t>https://www.indeed.com/viewjob?jk=e26c8b42dcd2f366</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2224a0c3978e6c38</t>
+          <t>https://www.indeed.com/viewjob?jk=712e8c299b3256ab</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=732c6c249f9d73c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f0229878a0d1503c</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69acac44ec199716</t>
+          <t>https://www.indeed.com/viewjob?jk=2479d8bb3713b04b</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122385d4dadbc41e</t>
+          <t>https://www.indeed.com/viewjob?jk=684321b06ebc10db</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917e38446999456c</t>
+          <t>https://www.indeed.com/viewjob?jk=888104a1629976bd</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c34b9216cdad10</t>
+          <t>https://www.indeed.com/viewjob?jk=62c2b94110d9cab5</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26c8b42dcd2f366</t>
+          <t>https://www.indeed.com/viewjob?jk=c18f439127c3b09d</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712e8c299b3256ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0229878a0d1503c</t>
+          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Jessup, MD, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2479d8bb3713b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684321b06ebc10db</t>
+          <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer - Active IQ Engineering</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=888104a1629976bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c2b94110d9cab5</t>
+          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c18f439127c3b09d</t>
+          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Engineering Applications</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,925 +6086,15 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ba3224629290a</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a92dacb6f0c06e</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>WY, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8777c1f859facbd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>MS, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc56720f97140d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90e498a115d128d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>WA, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8c2864f998fc6af</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>LA, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb86b3b19b4a8068</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>WI, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00b790d93392a179</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>MT, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=662e9fa60bd06133</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99d9cd4813e4e05f</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>CT, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b101e90c86c4fe4</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f75f93a5375c0579</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>WV, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc953ebe610d8912</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>ID, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=544b450a5ce07df4</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98bc7ef959a956c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>MD, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=360f723cdd8aa089</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Inabia Software &amp; Consulting Inc.</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9277248c547d05a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>UserGems</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, Scala, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9835c6151bce1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - Active IQ Engineering</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Application Developer</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>California Institute of Technology</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Pasadena, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, GCP, Hive, PostgreSQL, CI/CD, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb4f31db86d8854</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>AeroVironment</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Jessup, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Recursion Technologies, Inc</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Software Engineer, Engineering Applications</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
         </is>

--- a/results/job_matches_2026-06-11.xlsx
+++ b/results/job_matches_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Data Engineer - Bilingual Mandarin required</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e12084d35df615</t>
+          <t>https://www.indeed.com/viewjob?jk=bda129dc1d7139ca</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer-Marketing Technology</t>
+          <t>Data Engineer - Bilingual Mandarin required</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Foxit</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
+          <t>https://www.indeed.com/viewjob?jk=718307efaaa14959</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Development/Data Engineer</t>
+          <t>Data Engineer-Marketing Technology</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Foxit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
+          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Sr. Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Personalis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d09a1b90b86ef4e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb348c14b73d98a3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Medallion Architecture, GCP, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ffb50aa63952c2</t>
+          <t>https://www.indeed.com/viewjob?jk=444d7dbb36b2d6fc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development/Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=99ffb50aa63952c2</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
+          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
+          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
+          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
+          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
+          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
+          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
+          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
+          <t>Software Engineer II - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=1460aeeac19aef46</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer/Associate</t>
+          <t>DevOps Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Seattle Children's</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe630ebf9cbab80</t>
+          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid Eligible*)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d1491ce2afe6000a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer/Associate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Seattle Children's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe630ebf9cbab80</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Platform Architect</t>
+          <t>Senior Data Engineer (Hybrid Eligible*)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State of Arizona</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Informatica PowerCenter</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,129 +1476,129 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
+          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Inn-Flow Inc.</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
+          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
+          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Enterprise Data &amp; AI Platform Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>State of Arizona</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec9eccd457d1c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>o9 Solutions</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec9eccd457d1c7e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>o9 Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
+          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belews Creek, NC, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Data &amp; Analytics</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
+          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architecture – Advisor II</t>
+          <t>AWS MLOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
+          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
+          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
+          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
+          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
+          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
+          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
+          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
+          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
+          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
+          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
+          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
+          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
+          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
+          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
+          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
+          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
+          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
         </is>
       </c>
     </row>
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Analyst, Enterprise Data</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>MCLEOD SOFTWARE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
+          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Engineer with Python and React - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer with Python and React - Remote</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Analytics Data Engineer</t>
+          <t>Back-End Developer – Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, Scala, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
+          <t>https://www.indeed.com/viewjob?jk=323c21bf380dde66</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Analytics Engineer, AV Safety Engineering</t>
+          <t>Sr Data Architect, Databricks</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala, Kafka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
+          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Appian Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
+          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Back-End Developer – Remote</t>
+          <t>Database Platform Distinguished Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Scala, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323c21bf380dde66</t>
+          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Data Architect, Databricks</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Database Platform Distinguished Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,129 +3681,129 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
+          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=74d3e7e600902d7a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer, Financial Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dda4e17d3658df2</t>
+          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac20b554f3336983</t>
+          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>AlpacaJapan株式会社</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>Google Cloud Platform, GCP, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
+          <t>https://www.indeed.com/viewjob?jk=45b7132352f20af8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Product Engineer Data &amp; AI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AlpacaJapan株式会社</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b7132352f20af8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Product Engineer Data &amp; AI</t>
+          <t>ETL Developer - On-Site Contract</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site Contract</t>
+          <t>Identity Management Engineer III</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
+          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Junior Data Platform Administrator</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>MERS Missouri Goodwill Industries</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfba46a758bb1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=44bb3c31f7951efa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Identity Management Engineer III</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tulane University</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Sr. AI &amp; Data Engineer–Trading Analytics</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Shell Energy Retail</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,42 +4231,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
+          <t>https://www.indeed.com/viewjob?jk=f379cc52c6dc1b7b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Sr. Data Engineer (Charlotte, NC)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
+          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. AI &amp; Data Engineer–Trading Analytics</t>
+          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Shell Energy Retail</t>
+          <t>Zillow</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f379cc52c6dc1b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Zillow</t>
+          <t>AlpacaJapan株式会社</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f9bcf7a0cd9dbd</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BI Developer II</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sound Physicians</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34aa94cc9031fce2</t>
+          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AlpacaJapan株式会社</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f9bcf7a0cd9dbd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4446,29 +4446,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
+          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Tax Platform</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AlpacaJapan株式会社</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6ade65b566a785</t>
+          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76841faa3e2ec24</t>
+          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jessup, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6cd27db279cc95e</t>
+          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Software Application Developer II</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87468e85f996fc02</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Software Application Developer II</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93a7daa5f60c1ca</t>
+          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer - Active IQ Engineering</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9170b1fc1f9c04</t>
+          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b31324b6d66182</t>
+          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ac051678a5d39e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Engineering Applications</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3958fe987565e7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20575479ac0054a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Walkme</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,1172 +4931,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04bb514886baf37e</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab4b92177ab2a8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>ND, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce41d6460ea15565</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=539827ac7f0eff42</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60cc7bd7dd2de932</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>SD, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4199a58d952d0b71</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>DE, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b27686d3fff222ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e757b3e935e868</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea516f27762f34d</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf1b37c46622cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b093a06e94f20f9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d5617614ed464167</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2224a0c3978e6c38</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=732c6c249f9d73c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>HI, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69acac44ec199716</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=122385d4dadbc41e</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=917e38446999456c</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>VT, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96c34b9216cdad10</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>KS, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e26c8b42dcd2f366</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=712e8c299b3256ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0229878a0d1503c</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2479d8bb3713b04b</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>NV, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=684321b06ebc10db</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>NE, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=888104a1629976bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>SC, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62c2b94110d9cab5</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c18f439127c3b09d</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>AeroVironment</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Jessup, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Recursion Technologies, Inc</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - Active IQ Engineering</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Software Engineer, Engineering Applications</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
+          <t>https://www.indeed.com/viewjob?jk=1af1cdb9613b93fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-11.xlsx
+++ b/results/job_matches_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer-Marketing Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Foxit</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
+          <t>https://www.indeed.com/viewjob?jk=f94a8c00b79278f0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer-Marketing Technology</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Personalis</t>
+          <t>Foxit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb348c14b73d98a3</t>
+          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Sr. Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>Personalis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Medallion Architecture, GCP, Hadoop, Hive, Spark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444d7dbb36b2d6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=bb348c14b73d98a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Development/Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Medallion Architecture, GCP, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
+          <t>https://www.indeed.com/viewjob?jk=444d7dbb36b2d6fc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Development/Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,52 +696,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ffb50aa63952c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=99ffb50aa63952c2</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
+          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
+          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
+          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
+          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1460aeeac19aef46</t>
+          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Infrastructure</t>
+          <t>Software Engineer II - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,104 +1361,104 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
+          <t>https://www.indeed.com/viewjob?jk=1460aeeac19aef46</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, HBase, Spark</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1491ce2afe6000a</t>
+          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer/Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Seattle Children's</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe630ebf9cbab80</t>
+          <t>https://www.indeed.com/viewjob?jk=d1491ce2afe6000a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid Eligible*)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>MEDecision</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
+          <t>https://www.indeed.com/viewjob?jk=19beaee823c8d513</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer/Associate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Seattle Children's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe630ebf9cbab80</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
+          <t>Senior Data Engineer (Hybrid Eligible*)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
+          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Platform Architect</t>
+          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State of Arizona</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Informatica PowerCenter</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
+          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Riot Platforms, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>Redshift, Timestream, RDS, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb33b9b74da3225</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Inn-Flow Inc.</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec9eccd457d1c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>o9 Solutions</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
+          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
+          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec9eccd457d1c7e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I2E Consulting Pvt Ltd</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650af1c5e8c39884</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>o9 Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,304 +1861,304 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
+          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b152b5aa55d165</t>
+          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9873a5dcfe8027b5</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>I2E Consulting Pvt Ltd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0edad65551ccdff</t>
+          <t>https://www.indeed.com/viewjob?jk=650af1c5e8c39884</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c249c08b74171</t>
+          <t>https://www.indeed.com/viewjob?jk=47abd28c0aa248a7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9bbdc8248adbd</t>
+          <t>https://www.indeed.com/viewjob?jk=973ffbc88d0c427a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf0524e41351a6c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=b91c9d41b3a88a9c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b152b5aa55d165</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9873a5dcfe8027b5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b0edad65551ccdff</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=613c249c08b74171</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Software, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,77 +2306,77 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
+          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Analyst, Enterprise Data</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>MCLEOD SOFTWARE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Engineer with Python and React - Remote</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Back-End Developer – Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, Scala, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
+          <t>https://www.indeed.com/viewjob?jk=323c21bf380dde66</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Database Platform Distinguished Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
+          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr Data Architect, Databricks</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala, Kafka</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,277 +2666,277 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
+          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Appian Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
+          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
+          <t>https://www.indeed.com/viewjob?jk=74d3e7e600902d7a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Texas Farm Bureau and Affiliated Companies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
+          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Product Engineer Data &amp; AI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>ETL Developer - On-Site Contract</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,137 +2981,137 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
+          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
+          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Technology Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Lamb Weston</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,207 +3121,207 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
+          <t>https://www.indeed.com/viewjob?jk=819a863aec01dded</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
+          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Platform Engineer (Manufacturing)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr. Data Engineer (Charlotte, NC)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
+          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>AlpacaJapan株式会社</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f9bcf7a0cd9dbd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
+          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Analyst, Enterprise Data</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MCLEOD SOFTWARE</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer with Python and React - Remote</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dac519c3d40790</t>
+          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Back-End Developer – Remote</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Scala, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323c21bf380dde66</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Data Architect, Databricks</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jessup, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Appian Developer</t>
+          <t>IT Software Application Developer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Makpar Corporation</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Database Platform Distinguished Engineer</t>
+          <t>IT Software Application Developer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
+          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Full Stack Engineer - Active IQ Engineering</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,1265 +3681,40 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Walkme</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74d3e7e600902d7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>AssetMark</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>AlpacaJapan株式会社</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b7132352f20af8</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Product Engineer Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Sifted</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>ETL Developer - On-Site Contract</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Arctiq</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Duluth, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Identity Management Engineer III</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Availity, LLC.</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35969c0f5a1196e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Junior Data Platform Administrator</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>MERS Missouri Goodwill Industries</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44bb3c31f7951efa</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>DevOps &amp; Tools Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Qode</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>DevOps &amp; Tools Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Qode</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>DevOps &amp; Tools Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Qode</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Camas, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Technology Data Analyst</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Lamb Weston</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=819a863aec01dded</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Tulane University</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2618a71765f12c</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Sr. AI &amp; Data Engineer–Trading Analytics</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Shell Energy Retail</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f379cc52c6dc1b7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer (Charlotte, NC)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Zillow</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MLflow, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>AlpacaJapan株式会社</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f9bcf7a0cd9dbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Central Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Cloud Engineer II</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>CoorsTek</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Golden, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7366c85417c3b87e</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Enterprise Data Architect</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Rochester Electronics</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Newburyport, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Associate Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Presidio</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>AeroVironment</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Jessup, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, ETL, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>IT Software Application Developer II</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>IT Software Application Developer II</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - Active IQ Engineering</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Software Engineer, Engineering Applications</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Recursion Technologies, Inc</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Walkme</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1af1cdb9613b93fd</t>
         </is>
